--- a/data/trans_dic/P33B_R5-Clase-trans_dic.xlsx
+++ b/data/trans_dic/P33B_R5-Clase-trans_dic.xlsx
@@ -549,17 +549,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>7,42%</t>
+          <t>7,19%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>9,03%</t>
+          <t>9,47%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>8,18%</t>
+          <t>8,26%</t>
         </is>
       </c>
     </row>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>5,52; 9,88</t>
+          <t>5,28; 9,31</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>7,05; 11,46</t>
+          <t>7,33; 11,82</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>6,57; 9,82</t>
+          <t>6,76; 9,95</t>
         </is>
       </c>
     </row>
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>6,74%</t>
+          <t>6,62%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>6,91%</t>
+          <t>7,45%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>6,82%</t>
+          <t>7,01%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>4,86; 9,3</t>
+          <t>4,76; 8,83</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>5,03; 9,35</t>
+          <t>5,45; 9,67</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>5,45; 8,29</t>
+          <t>5,67; 8,84</t>
         </is>
       </c>
     </row>
@@ -649,17 +649,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>5,24%</t>
+          <t>7,94%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>15,01%</t>
+          <t>14,79%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>7,19%</t>
+          <t>9,89%</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1,85; 9,16</t>
+          <t>5,92; 10,66</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>10,83; 19,69</t>
+          <t>10,42; 18,88</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>3,11; 10,74</t>
+          <t>8,04; 12,07</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>7,67%</t>
+          <t>7,8%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>7,21%</t>
+          <t>9,12%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>7,45%</t>
+          <t>8,37%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>6,22; 9,48</t>
+          <t>6,51; 9,71</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>3,54; 9,66</t>
+          <t>7,58; 10,96</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>5,2; 8,76</t>
+          <t>7,29; 9,57</t>
         </is>
       </c>
     </row>
@@ -749,17 +749,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>5,76%</t>
+          <t>5,41%</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>16,08%</t>
+          <t>17,57%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>12,36%</t>
+          <t>12,64%</t>
         </is>
       </c>
     </row>
@@ -772,24 +772,24 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>4,21; 8,01</t>
+          <t>3,81; 7,34</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>12,2; 19,5</t>
+          <t>15,61; 19,72</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>10,02; 14,2</t>
+          <t>11,37; 14,24</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -799,17 +799,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>2,88%</t>
+          <t>2,72%</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>16,21%</t>
+          <t>16,14%</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>13,01%</t>
+          <t>13,19%</t>
         </is>
       </c>
     </row>
@@ -822,17 +822,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,92; 9,3</t>
+          <t>0,89; 8,61</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>14,04; 18,38</t>
+          <t>14,08; 18,23</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>11,24; 14,82</t>
+          <t>11,46; 15,23</t>
         </is>
       </c>
     </row>
@@ -849,17 +849,17 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>6,42%</t>
+          <t>6,82%</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>11,77%</t>
+          <t>12,83%</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>9,17%</t>
+          <t>9,9%</t>
         </is>
       </c>
     </row>
@@ -872,17 +872,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>4,92; 7,38</t>
+          <t>6,08; 7,78</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>9,34; 13,03</t>
+          <t>11,88; 13,72</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>7,79; 9,99</t>
+          <t>9,29; 10,51</t>
         </is>
       </c>
     </row>
@@ -1009,17 +1009,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>37492</t>
+          <t>39597</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>40419</t>
+          <t>46246</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>77910</t>
+          <t>85843</t>
         </is>
       </c>
     </row>
@@ -1032,17 +1032,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>27864; 49914</t>
+          <t>29063; 51269</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>31533; 51265</t>
+          <t>35797; 57746</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>62579; 93565</t>
+          <t>70214; 103388</t>
         </is>
       </c>
     </row>
@@ -1082,17 +1082,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>30475</t>
+          <t>32012</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>26411</t>
+          <t>31461</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>56886</t>
+          <t>63473</t>
         </is>
       </c>
     </row>
@@ -1105,17 +1105,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>21970; 42068</t>
+          <t>23010; 42674</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>19202; 35700</t>
+          <t>23029; 40873</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>45433; 69145</t>
+          <t>51318; 80061</t>
         </is>
       </c>
     </row>
@@ -1155,17 +1155,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>35027</t>
+          <t>37462</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>25056</t>
+          <t>27724</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>60084</t>
+          <t>65186</t>
         </is>
       </c>
     </row>
@@ -1178,17 +1178,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>12367; 61244</t>
+          <t>27940; 50261</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>18071; 32868</t>
+          <t>19533; 35407</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>25970; 89665</t>
+          <t>53011; 79553</t>
         </is>
       </c>
     </row>
@@ -1228,17 +1228,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>79341</t>
+          <t>88311</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>70518</t>
+          <t>78520</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>149860</t>
+          <t>166831</t>
         </is>
       </c>
     </row>
@@ -1251,17 +1251,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>64348; 98056</t>
+          <t>73632; 109928</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>34624; 94382</t>
+          <t>65263; 94310</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>104614; 176274</t>
+          <t>145330; 190725</t>
         </is>
       </c>
     </row>
@@ -1301,17 +1301,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>27255</t>
+          <t>30643</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>134938</t>
+          <t>145827</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>162192</t>
+          <t>176470</t>
         </is>
       </c>
     </row>
@@ -1324,24 +1324,24 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>19937; 37868</t>
+          <t>21577; 41513</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>102389; 163565</t>
+          <t>129601; 163688</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>131410; 186284</t>
+          <t>158724; 198755</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -1374,17 +1374,17 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>6931</t>
+          <t>6454</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>123396</t>
+          <t>136225</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>130327</t>
+          <t>142679</t>
         </is>
       </c>
     </row>
@@ -1397,17 +1397,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>2210; 22378</t>
+          <t>2100; 20420</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>106899; 139971</t>
+          <t>118876; 153937</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>112651; 148478</t>
+          <t>123967; 164723</t>
         </is>
       </c>
     </row>
@@ -1447,17 +1447,17 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>216521</t>
+          <t>234479</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>420737</t>
+          <t>466003</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>637258</t>
+          <t>700482</t>
         </is>
       </c>
     </row>
@@ -1470,17 +1470,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>166082; 249038</t>
+          <t>209071; 267818</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>333661; 465887</t>
+          <t>431744; 498573</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>541236; 694106</t>
+          <t>657490; 743702</t>
         </is>
       </c>
     </row>
